--- a/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1306"/>
+  <dimension ref="A1:C1314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20078,6 +20078,134 @@
         <v>94</v>
       </c>
     </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t xml:space="preserve">de oliveira m 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1307" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">allatin m 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1308" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">demianchuk s 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1309" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fischer d 
+  can </t>
+        </is>
+      </c>
+      <c r="C1310" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">gonzales g 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1311" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">unkel t 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1312" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">marrufo j 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1313" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">chapman a 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1314" t="n">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1314"/>
+  <dimension ref="A1:C1316"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20206,6 +20206,38 @@
         <v>167</v>
       </c>
     </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ford t 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1315" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dickerson j 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1316" t="n">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1316"/>
+  <dimension ref="A1:C1318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20238,6 +20238,38 @@
         <v>168</v>
       </c>
     </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">soldier field
+  chicago  il </t>
+        </is>
+      </c>
+      <c r="C1317" t="n">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">children s mercy park
+  kansas city  ks </t>
+        </is>
+      </c>
+      <c r="C1318" t="n">
+        <v>95</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1318"/>
+  <dimension ref="A1:C1330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20270,6 +20270,186 @@
         <v>95</v>
       </c>
     </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="C1319" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="C1320" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="C1321" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="C1322" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="C1323" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="C1324" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="C1325" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="C1326" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="C1327" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+      <c r="C1328" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="C1329" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="C1330" t="n">
+        <v>189</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1330"/>
+  <dimension ref="A1:C1336"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20450,6 +20450,96 @@
         <v>189</v>
       </c>
     </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="C1331" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="C1332" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="C1333" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+      <c r="C1334" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="C1335" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="C1336" t="n">
+        <v>190</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1336"/>
+  <dimension ref="A1:C1364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20540,6 +20540,426 @@
         <v>190</v>
       </c>
     </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="C1337" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="C1338" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="C1339" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="C1340" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="C1341" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="C1342" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="C1343" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="C1344" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="C1345" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="C1346" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="C1347" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="C1348" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="C1349" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="C1350" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="C1351" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="C1352" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="C1353" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="C1354" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="C1355" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="C1356" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="C1357" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="C1358" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="C1359" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="C1360" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="C1361" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="C1362" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="C1363" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="C1364" t="n">
+        <v>191</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1318"/>
+  <dimension ref="A1:C1345"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20270,6 +20270,411 @@
         <v>95</v>
       </c>
     </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="C1319" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="C1320" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="C1321" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="C1322" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="C1323" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="C1324" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="C1325" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="C1326" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="C1327" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="C1328" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="C1329" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="C1330" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="C1331" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="C1332" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="C1333" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+      <c r="C1334" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="C1335" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="C1336" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="C1337" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="C1338" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="C1339" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="C1340" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>022mBmSn</t>
+        </is>
+      </c>
+      <c r="C1341" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="C1342" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="C1343" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="C1344" t="n">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Uw6sTk0t</t>
+        </is>
+      </c>
+      <c r="C1345" t="n">
+        <v>189</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1345"/>
+  <dimension ref="A1:C1376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20675,6 +20675,474 @@
         <v>189</v>
       </c>
     </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">corbyn m 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1346" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">surgan j 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1347" t="n">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">heart health park
+  sacramento  ca </t>
+        </is>
+      </c>
+      <c r="C1348" t="n">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>vucevHGn</t>
+        </is>
+      </c>
+      <c r="C1349" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="C1350" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="C1351" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="C1352" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="C1353" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="C1354" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="C1355" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="C1356" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="C1357" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="C1358" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="C1359" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>6V8Ndys8</t>
+        </is>
+      </c>
+      <c r="C1360" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="C1361" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="C1362" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>MRdhQQTs</t>
+        </is>
+      </c>
+      <c r="C1363" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="C1364" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+      <c r="C1365" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="C1366" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="C1367" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="C1368" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="C1369" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+      <c r="C1370" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="C1371" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>Onn3tCA5</t>
+        </is>
+      </c>
+      <c r="C1372" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="C1373" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="C1374" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="C1375" t="n">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>zoZ995af</t>
+        </is>
+      </c>
+      <c r="C1376" t="n">
+        <v>190</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1376"/>
+  <dimension ref="A1:C1377"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21143,6 +21143,22 @@
         <v>190</v>
       </c>
     </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">fierro r 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1377" t="n">
+        <v>170</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1377"/>
+  <dimension ref="A1:C1418"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21159,6 +21159,625 @@
         <v>170</v>
       </c>
     </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>Sd7snoa0</t>
+        </is>
+      </c>
+      <c r="C1378" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="C1379" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>dp6AQn9c</t>
+        </is>
+      </c>
+      <c r="C1380" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>l6eEjGlO</t>
+        </is>
+      </c>
+      <c r="C1381" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>86yPt28f</t>
+        </is>
+      </c>
+      <c r="C1382" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>GzULyFoh</t>
+        </is>
+      </c>
+      <c r="C1383" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>z9ZXDy6o</t>
+        </is>
+      </c>
+      <c r="C1384" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="C1385" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>roEEsq76</t>
+        </is>
+      </c>
+      <c r="C1386" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>6BusaLE3</t>
+        </is>
+      </c>
+      <c r="C1387" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>K4zRMgTN</t>
+        </is>
+      </c>
+      <c r="C1388" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="C1389" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="C1390" t="n">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ndiaye a 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1391" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>bFuhdIb3</t>
+        </is>
+      </c>
+      <c r="C1392" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>WWvwigh8</t>
+        </is>
+      </c>
+      <c r="C1393" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>lAVQ9RGh</t>
+        </is>
+      </c>
+      <c r="C1394" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>UFWZoX9L</t>
+        </is>
+      </c>
+      <c r="C1395" t="n">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>jBBpU7Y0</t>
+        </is>
+      </c>
+      <c r="C1396" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>MFwJSk8d</t>
+        </is>
+      </c>
+      <c r="C1397" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>xA45kovo</t>
+        </is>
+      </c>
+      <c r="C1398" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="C1399" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>nJ01AhXP</t>
+        </is>
+      </c>
+      <c r="C1400" t="n">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>2PIEeC7j</t>
+        </is>
+      </c>
+      <c r="C1401" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="C1402" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>EgT3xN3S</t>
+        </is>
+      </c>
+      <c r="C1403" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>bFuhdIb3</t>
+        </is>
+      </c>
+      <c r="C1404" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>EqKWmJfM</t>
+        </is>
+      </c>
+      <c r="C1405" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>UL7r7duf</t>
+        </is>
+      </c>
+      <c r="C1406" t="n">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t xml:space="preserve">touchan r 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1407" t="n">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">montero r 
+  cos </t>
+        </is>
+      </c>
+      <c r="C1408" t="n">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>URfp4iBR</t>
+        </is>
+      </c>
+      <c r="C1409" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>txm4BKVR</t>
+        </is>
+      </c>
+      <c r="C1410" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">snyder t 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1411" t="n">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>CfE5JcGF</t>
+        </is>
+      </c>
+      <c r="C1412" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>KtuTuMN0</t>
+        </is>
+      </c>
+      <c r="C1413" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>K4FYmLD9</t>
+        </is>
+      </c>
+      <c r="C1414" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="C1415" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>rJ9D8rzj</t>
+        </is>
+      </c>
+      <c r="C1416" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>pKAODsPO</t>
+        </is>
+      </c>
+      <c r="C1417" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>tOpyQa24</t>
+        </is>
+      </c>
+      <c r="C1418" t="n">
+        <v>197</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1418"/>
+  <dimension ref="A1:C1425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21778,6 +21778,113 @@
         <v>197</v>
       </c>
     </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1419" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villarreal a 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1420" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>rXawJi8t</t>
+        </is>
+      </c>
+      <c r="C1421" t="n">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>6gpXy3vi</t>
+        </is>
+      </c>
+      <c r="C1422" t="n">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>WSL0wFD4</t>
+        </is>
+      </c>
+      <c r="C1423" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="C1424" t="n">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>6LuGZiZI</t>
+        </is>
+      </c>
+      <c r="C1425" t="n">
+        <v>199</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/usa/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1425"/>
+  <dimension ref="A1:C1427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21885,6 +21885,37 @@
         <v>199</v>
       </c>
     </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bazakos f 
+  usa </t>
+        </is>
+      </c>
+      <c r="C1426" t="n">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>63fk89be</t>
+        </is>
+      </c>
+      <c r="C1427" t="n">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
